--- a/01-Field-Discovery/reports/figures-03/课题03_图表.xlsx
+++ b/01-Field-Discovery/reports/figures-03/课题03_图表.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图1_下载速率" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSSI" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,7 +136,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>课题03 · 各点位下载速率均值（MB/s）</a:t>
+              <a:t>课题03 · 各点位 RSSI 均值</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -156,7 +151,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'图1_下载速率'!B1</f>
+              <f>'RSSI'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -166,19 +161,19 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'图1_下载速率'!$A$2:$A$9</f>
+              <f>'RSSI'!$A$2:$A$10</f>
             </numRef>
             <strRef>
-              <f>'图1_下载速率'!$A$2:$A$9</f>
+              <f>'RSSI'!$A$2:$A$10</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'图1_下载速率'!$B$2:$B$9</f>
+              <f>'RSSI'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="40"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -189,21 +184,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>点位</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -213,6 +193,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0"/>
+          <min val="-100"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -226,7 +208,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>MB/s</a:t>
+                  <a:t>RSSI (dBm)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -559,11 +541,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,18 +556,18 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>下载均值(MB/s)</t>
+          <t>RSSI均值(dBm)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>大厅</t>
+          <t>5楼大厅</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.84</v>
+        <v>-48.25</v>
       </c>
     </row>
     <row r="3">
@@ -595,47 +577,47 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.09</v>
+        <v>-53.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5楼电梯口</t>
+          <t>两楼连接处</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.65</v>
+        <v>-41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>电梯运行中</t>
+          <t>5楼电梯口</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-65.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>两楼连接处</t>
+          <t>5楼厕所</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.76</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>厕所</t>
+          <t>8楼电梯口</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.49</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="8">
@@ -645,269 +627,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.54</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8楼电梯口</t>
+          <t>2楼电梯内部</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.23</v>
+        <v>-87.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>电梯运行中</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>点位编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>点位名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>下载均值(MB/s)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>大厅</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>露台</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5楼电梯口</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>电梯运行中</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>盲区</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>两楼连接处</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>厕所</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2楼电梯口</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8楼电梯口</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>